--- a/data/nzd0599/nzd0599.xlsx
+++ b/data/nzd0599/nzd0599.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L682"/>
+  <dimension ref="A1:L686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29014,7 +29014,7 @@
         <v>191.77</v>
       </c>
       <c r="H681" t="n">
-        <v>192.59</v>
+        <v>193.47</v>
       </c>
       <c r="I681" t="n">
         <v>184.69</v>
@@ -29056,7 +29056,7 @@
         <v>191.78</v>
       </c>
       <c r="H682" t="n">
-        <v>192.43</v>
+        <v>193.47</v>
       </c>
       <c r="I682" t="n">
         <v>184.56</v>
@@ -29068,6 +29068,174 @@
         <v>196.67</v>
       </c>
       <c r="L682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>178.28</v>
+      </c>
+      <c r="C683" t="n">
+        <v>174.39</v>
+      </c>
+      <c r="D683" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="E683" t="n">
+        <v>185.46</v>
+      </c>
+      <c r="F683" t="n">
+        <v>188.32</v>
+      </c>
+      <c r="G683" t="n">
+        <v>191.74</v>
+      </c>
+      <c r="H683" t="n">
+        <v>198.62</v>
+      </c>
+      <c r="I683" t="n">
+        <v>184.94</v>
+      </c>
+      <c r="J683" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="K683" t="n">
+        <v>196.57</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="C684" t="n">
+        <v>175.52</v>
+      </c>
+      <c r="D684" t="n">
+        <v>182.21</v>
+      </c>
+      <c r="E684" t="n">
+        <v>186.67</v>
+      </c>
+      <c r="F684" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="G684" t="n">
+        <v>193.13</v>
+      </c>
+      <c r="H684" t="n">
+        <v>200.12</v>
+      </c>
+      <c r="I684" t="n">
+        <v>187.31</v>
+      </c>
+      <c r="J684" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="K684" t="n">
+        <v>198.89</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="C685" t="n">
+        <v>175.69</v>
+      </c>
+      <c r="D685" t="n">
+        <v>182.42</v>
+      </c>
+      <c r="E685" t="n">
+        <v>187.05</v>
+      </c>
+      <c r="F685" t="n">
+        <v>189.86</v>
+      </c>
+      <c r="G685" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="H685" t="n">
+        <v>199.87</v>
+      </c>
+      <c r="I685" t="n">
+        <v>188</v>
+      </c>
+      <c r="J685" t="n">
+        <v>188.09</v>
+      </c>
+      <c r="K685" t="n">
+        <v>199.24</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>181.52</v>
+      </c>
+      <c r="C686" t="n">
+        <v>175.52</v>
+      </c>
+      <c r="D686" t="n">
+        <v>182.21</v>
+      </c>
+      <c r="E686" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="F686" t="n">
+        <v>189.67</v>
+      </c>
+      <c r="G686" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="H686" t="n">
+        <v>199.01</v>
+      </c>
+      <c r="I686" t="n">
+        <v>187.91</v>
+      </c>
+      <c r="J686" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="K686" t="n">
+        <v>199.05</v>
+      </c>
+      <c r="L686" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29084,7 +29252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B699"/>
+  <dimension ref="A1:B703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36077,6 +36245,46 @@
       </c>
       <c r="B699" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -36239,28 +36447,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2430043582692371</v>
+        <v>0.2381630157287841</v>
       </c>
       <c r="J2" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K2" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09375112111837458</v>
+        <v>0.09115390775382692</v>
       </c>
       <c r="M2" t="n">
-        <v>4.561815068479111</v>
+        <v>4.559738496244029</v>
       </c>
       <c r="N2" t="n">
-        <v>32.65079651543233</v>
+        <v>32.57648790906145</v>
       </c>
       <c r="O2" t="n">
-        <v>5.7140875488071</v>
+        <v>5.707581616504616</v>
       </c>
       <c r="P2" t="n">
-        <v>178.4039507072486</v>
+        <v>178.4554918475803</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36311,28 +36519,28 @@
         <v>0.0997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3397145005283524</v>
+        <v>0.3411823304447705</v>
       </c>
       <c r="J3" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K3" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2282402721371442</v>
+        <v>0.2319607347137653</v>
       </c>
       <c r="M3" t="n">
-        <v>3.776590326952249</v>
+        <v>3.761772811940197</v>
       </c>
       <c r="N3" t="n">
-        <v>22.3209486419019</v>
+        <v>22.20151325151472</v>
       </c>
       <c r="O3" t="n">
-        <v>4.724505121375349</v>
+        <v>4.71184817789312</v>
       </c>
       <c r="P3" t="n">
-        <v>164.8184658031829</v>
+        <v>164.802831437943</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36383,28 +36591,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6139044336705518</v>
+        <v>0.6189786964891744</v>
       </c>
       <c r="J4" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K4" t="n">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6651205214210241</v>
+        <v>0.6692474010329146</v>
       </c>
       <c r="M4" t="n">
-        <v>2.666159531356081</v>
+        <v>2.676149027554868</v>
       </c>
       <c r="N4" t="n">
-        <v>10.88328193126382</v>
+        <v>10.93632801996328</v>
       </c>
       <c r="O4" t="n">
-        <v>3.298981953764497</v>
+        <v>3.307011947357203</v>
       </c>
       <c r="P4" t="n">
-        <v>160.9000596312998</v>
+        <v>160.8460734669988</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36455,28 +36663,28 @@
         <v>0.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6243090623438847</v>
+        <v>0.6308047521318622</v>
       </c>
       <c r="J5" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K5" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7243050437680946</v>
+        <v>0.7265652913621052</v>
       </c>
       <c r="M5" t="n">
-        <v>2.292055611308478</v>
+        <v>2.309929838369937</v>
       </c>
       <c r="N5" t="n">
-        <v>8.497470191302691</v>
+        <v>8.637571502310648</v>
       </c>
       <c r="O5" t="n">
-        <v>2.915042056523832</v>
+        <v>2.938974566462025</v>
       </c>
       <c r="P5" t="n">
-        <v>163.9053201962167</v>
+        <v>163.8361795599803</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36527,28 +36735,28 @@
         <v>0.1228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5049452260870605</v>
+        <v>0.5127427621226641</v>
       </c>
       <c r="J6" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K6" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6597042897788987</v>
+        <v>0.6614484118188138</v>
       </c>
       <c r="M6" t="n">
-        <v>2.243596754540853</v>
+        <v>2.269104214499538</v>
       </c>
       <c r="N6" t="n">
-        <v>7.522987669487161</v>
+        <v>7.751192470586949</v>
       </c>
       <c r="O6" t="n">
-        <v>2.742806531545228</v>
+        <v>2.784096347216984</v>
       </c>
       <c r="P6" t="n">
-        <v>168.8572808805732</v>
+        <v>168.774243185891</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36599,28 +36807,28 @@
         <v>0.1034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4366991036487489</v>
+        <v>0.4433426892137817</v>
       </c>
       <c r="J7" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K7" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6189869160431192</v>
+        <v>0.6222206029002433</v>
       </c>
       <c r="M7" t="n">
-        <v>2.117290626698605</v>
+        <v>2.136145019767711</v>
       </c>
       <c r="N7" t="n">
-        <v>6.714561623668231</v>
+        <v>6.87406367687818</v>
       </c>
       <c r="O7" t="n">
-        <v>2.591247117445233</v>
+        <v>2.62184356453206</v>
       </c>
       <c r="P7" t="n">
-        <v>175.2534851596931</v>
+        <v>175.1827356490642</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36671,28 +36879,28 @@
         <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1119550360047446</v>
+        <v>0.126724589142735</v>
       </c>
       <c r="J8" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K8" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09400295347444343</v>
+        <v>0.1059706488280251</v>
       </c>
       <c r="M8" t="n">
-        <v>2.042392445814423</v>
+        <v>2.111669714263936</v>
       </c>
       <c r="N8" t="n">
-        <v>6.909827306981914</v>
+        <v>7.804202571926012</v>
       </c>
       <c r="O8" t="n">
-        <v>2.628655037653651</v>
+        <v>2.793600288503352</v>
       </c>
       <c r="P8" t="n">
-        <v>183.862657916761</v>
+        <v>183.7053978302829</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36743,28 +36951,28 @@
         <v>0.1005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05758351239439039</v>
+        <v>-0.05598858265665224</v>
       </c>
       <c r="J9" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K9" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01342981005575006</v>
+        <v>0.01284946444924207</v>
       </c>
       <c r="M9" t="n">
-        <v>3.028647670576408</v>
+        <v>3.021243485579551</v>
       </c>
       <c r="N9" t="n">
-        <v>13.93314204319538</v>
+        <v>13.87196140418752</v>
       </c>
       <c r="O9" t="n">
-        <v>3.732712424389987</v>
+        <v>3.724508209708702</v>
       </c>
       <c r="P9" t="n">
-        <v>187.1898794722542</v>
+        <v>187.1728840705224</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36815,28 +37023,28 @@
         <v>0.1107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1212000477045383</v>
+        <v>-0.1196309400577381</v>
       </c>
       <c r="J10" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K10" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07186684608338934</v>
+        <v>0.07080258916178495</v>
       </c>
       <c r="M10" t="n">
-        <v>2.690565659694339</v>
+        <v>2.687137015117405</v>
       </c>
       <c r="N10" t="n">
-        <v>10.9041844513863</v>
+        <v>10.87149065553783</v>
       </c>
       <c r="O10" t="n">
-        <v>3.30214845992519</v>
+        <v>3.297194361201327</v>
       </c>
       <c r="P10" t="n">
-        <v>188.4284739384887</v>
+        <v>188.4118066921846</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36887,28 +37095,28 @@
         <v>0.1286</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01322422444644462</v>
+        <v>0.02021934450133092</v>
       </c>
       <c r="J11" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K11" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0005774588300971883</v>
+        <v>0.001348738306890751</v>
       </c>
       <c r="M11" t="n">
-        <v>3.33277068457993</v>
+        <v>3.353156701691572</v>
       </c>
       <c r="N11" t="n">
-        <v>17.39700323844432</v>
+        <v>17.52118684735828</v>
       </c>
       <c r="O11" t="n">
-        <v>4.170971498157751</v>
+        <v>4.185831679291259</v>
       </c>
       <c r="P11" t="n">
-        <v>191.8993704078641</v>
+        <v>191.825134533692</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36946,7 +37154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L682"/>
+  <dimension ref="A1:L686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79103,7 +79311,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>-36.8230914557875,174.8096076578231</t>
+          <t>-36.82308704442394,174.8096158551504</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -79165,7 +79373,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>-36.823092257853546,174.80960616739983</t>
+          <t>-36.82308704442394,174.8096158551504</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -79184,6 +79392,254 @@
         </is>
       </c>
       <c r="L682" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-36.819508201756484,174.80658769528046</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-36.82013494029984,174.8070327506723</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-36.82071586894422,174.8075570149065</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-36.82131399044472,174.80807120455623</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-36.82190373167232,174.8085880009869</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-36.822491095695014,174.80910892888176</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>-36.82306122791045,174.80966382812647</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>-36.823728947131556,174.81003516967436</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>-36.82433508992316,174.81052286573265</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>-36.824851074309,174.8111788476162</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-36.81949551169162,174.80661246042885</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-36.820129471232136,174.80704343517985</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-36.820709782184544,174.8075695966481</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-36.821308031893146,174.80808256364915</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-36.821897773070624,174.80859936012294</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-36.82248427549831,174.8091219979847</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>-36.82305370853408,174.8096778008318</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>-36.8237170664448,174.81005724667472</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>-36.82431815068947,174.81055394964133</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>-36.82483727319694,174.8111983829599</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-36.819489699446514,174.80662380324216</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-36.820128648451956,174.8070450425835</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-36.82070880644432,174.80757161356834</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-36.821306160612274,174.8080861309672</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-36.821896147997236,174.8086024580688</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-36.82248216565302,174.80912604094414</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>-36.823054961763596,174.8096754720478</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>-36.82371360750992,174.81006367415455</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>-36.824311627818304,174.81056591926213</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>-36.82483519113235,174.81120133010165</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-36.819492508698445,174.8066183208826</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-36.820129471232136,174.80704343517985</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-36.820709782184544,174.8075695966481</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-36.82130788416044,174.80808284527953</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-36.82189708364556,174.808600674403</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-36.82248442269682,174.80912171591777</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>-36.82305927287275,174.80966746103013</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>-36.823714058675385,174.81006283578765</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>-36.824312993070514,174.81056341399284</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>-36.824836321395985,174.81119973022473</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0599/nzd0599.xlsx
+++ b/data/nzd0599/nzd0599.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29236,6 +29236,174 @@
         <v>199.05</v>
       </c>
       <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>180.76</v>
+      </c>
+      <c r="C687" t="n">
+        <v>175.81</v>
+      </c>
+      <c r="D687" t="n">
+        <v>182.54</v>
+      </c>
+      <c r="E687" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="F687" t="n">
+        <v>189.91</v>
+      </c>
+      <c r="G687" t="n">
+        <v>193.39</v>
+      </c>
+      <c r="H687" t="n">
+        <v>198.39</v>
+      </c>
+      <c r="I687" t="n">
+        <v>188.08</v>
+      </c>
+      <c r="J687" t="n">
+        <v>187.93</v>
+      </c>
+      <c r="K687" t="n">
+        <v>198.73</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>180.85</v>
+      </c>
+      <c r="C688" t="n">
+        <v>175.75</v>
+      </c>
+      <c r="D688" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="E688" t="n">
+        <v>186.84</v>
+      </c>
+      <c r="F688" t="n">
+        <v>190.03</v>
+      </c>
+      <c r="G688" t="n">
+        <v>193.22</v>
+      </c>
+      <c r="H688" t="n">
+        <v>198.13</v>
+      </c>
+      <c r="I688" t="n">
+        <v>188.44</v>
+      </c>
+      <c r="J688" t="n">
+        <v>188.02</v>
+      </c>
+      <c r="K688" t="n">
+        <v>198.8</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="C689" t="n">
+        <v>175.51</v>
+      </c>
+      <c r="D689" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="E689" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="F689" t="n">
+        <v>190</v>
+      </c>
+      <c r="G689" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="H689" t="n">
+        <v>197.82</v>
+      </c>
+      <c r="I689" t="n">
+        <v>188.27</v>
+      </c>
+      <c r="J689" t="n">
+        <v>187.89</v>
+      </c>
+      <c r="K689" t="n">
+        <v>198.83</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>180.26</v>
+      </c>
+      <c r="C690" t="n">
+        <v>175.24</v>
+      </c>
+      <c r="D690" t="n">
+        <v>182.63</v>
+      </c>
+      <c r="E690" t="n">
+        <v>185.85</v>
+      </c>
+      <c r="F690" t="n">
+        <v>189.36</v>
+      </c>
+      <c r="G690" t="n">
+        <v>192.87</v>
+      </c>
+      <c r="H690" t="n">
+        <v>197.46</v>
+      </c>
+      <c r="I690" t="n">
+        <v>187.97</v>
+      </c>
+      <c r="J690" t="n">
+        <v>187.85</v>
+      </c>
+      <c r="K690" t="n">
+        <v>198.58</v>
+      </c>
+      <c r="L690" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29252,7 +29420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B703"/>
+  <dimension ref="A1:B707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36285,6 +36453,46 @@
       </c>
       <c r="B703" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -36447,28 +36655,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2381630157287841</v>
+        <v>0.2333446440260231</v>
       </c>
       <c r="J2" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K2" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09115390775382692</v>
+        <v>0.08858949524464732</v>
       </c>
       <c r="M2" t="n">
-        <v>4.559738496244029</v>
+        <v>4.557865214621564</v>
       </c>
       <c r="N2" t="n">
-        <v>32.57648790906145</v>
+        <v>32.49220111257803</v>
       </c>
       <c r="O2" t="n">
-        <v>5.707581616504616</v>
+        <v>5.700193076780648</v>
       </c>
       <c r="P2" t="n">
-        <v>178.4554918475803</v>
+        <v>178.5069965365435</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36519,28 +36727,28 @@
         <v>0.0997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3411823304447705</v>
+        <v>0.3429105817570017</v>
       </c>
       <c r="J3" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K3" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2319607347137653</v>
+        <v>0.2359471303702564</v>
       </c>
       <c r="M3" t="n">
-        <v>3.761772811940197</v>
+        <v>3.748353689576303</v>
       </c>
       <c r="N3" t="n">
-        <v>22.20151325151472</v>
+        <v>22.08625803128373</v>
       </c>
       <c r="O3" t="n">
-        <v>4.71184817789312</v>
+        <v>4.699601901361831</v>
       </c>
       <c r="P3" t="n">
-        <v>164.802831437943</v>
+        <v>164.7843624278601</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36591,28 +36799,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6189786964891744</v>
+        <v>0.6246400388317364</v>
       </c>
       <c r="J4" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K4" t="n">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6692474010329146</v>
+        <v>0.6731514461222565</v>
       </c>
       <c r="M4" t="n">
-        <v>2.676149027554868</v>
+        <v>2.689065003885605</v>
       </c>
       <c r="N4" t="n">
-        <v>10.93632801996328</v>
+        <v>11.01781800813286</v>
       </c>
       <c r="O4" t="n">
-        <v>3.307011947357203</v>
+        <v>3.319309869254882</v>
       </c>
       <c r="P4" t="n">
-        <v>160.8460734669988</v>
+        <v>160.7856190791054</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36663,28 +36871,28 @@
         <v>0.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6308047521318622</v>
+        <v>0.6371063131407035</v>
       </c>
       <c r="J5" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K5" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7265652913621052</v>
+        <v>0.7289040052987708</v>
       </c>
       <c r="M5" t="n">
-        <v>2.309929838369937</v>
+        <v>2.32733728649261</v>
       </c>
       <c r="N5" t="n">
-        <v>8.637571502310648</v>
+        <v>8.768074121376173</v>
       </c>
       <c r="O5" t="n">
-        <v>2.938974566462025</v>
+        <v>2.9610933996374</v>
       </c>
       <c r="P5" t="n">
-        <v>163.8361795599803</v>
+        <v>163.7688633620556</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36735,28 +36943,28 @@
         <v>0.1228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5127427621226641</v>
+        <v>0.5207987715039039</v>
       </c>
       <c r="J6" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K6" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6614484118188138</v>
+        <v>0.6629150651310777</v>
       </c>
       <c r="M6" t="n">
-        <v>2.269104214499538</v>
+        <v>2.29740430887078</v>
       </c>
       <c r="N6" t="n">
-        <v>7.751192470586949</v>
+        <v>7.999687332095369</v>
       </c>
       <c r="O6" t="n">
-        <v>2.784096347216984</v>
+        <v>2.828371851807214</v>
       </c>
       <c r="P6" t="n">
-        <v>168.774243185891</v>
+        <v>168.6881394174622</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36807,28 +37015,28 @@
         <v>0.1034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4433426892137817</v>
+        <v>0.4500943797259051</v>
       </c>
       <c r="J7" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K7" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6222206029002433</v>
+        <v>0.6253370360541654</v>
       </c>
       <c r="M7" t="n">
-        <v>2.136145019767711</v>
+        <v>2.15595261355287</v>
       </c>
       <c r="N7" t="n">
-        <v>6.87406367687818</v>
+        <v>7.04020734083831</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62184356453206</v>
+        <v>2.653338904255977</v>
       </c>
       <c r="P7" t="n">
-        <v>175.1827356490642</v>
+        <v>175.1105723267216</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36879,28 +37087,28 @@
         <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.126724589142735</v>
+        <v>0.1388810254864987</v>
       </c>
       <c r="J8" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K8" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1059706488280251</v>
+        <v>0.1172007709671192</v>
       </c>
       <c r="M8" t="n">
-        <v>2.111669714263936</v>
+        <v>2.171062707229928</v>
       </c>
       <c r="N8" t="n">
-        <v>7.804202571926012</v>
+        <v>8.426921766314761</v>
       </c>
       <c r="O8" t="n">
-        <v>2.793600288503352</v>
+        <v>2.902916079791967</v>
       </c>
       <c r="P8" t="n">
-        <v>183.7053978302829</v>
+        <v>183.5754682338955</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36951,28 +37159,28 @@
         <v>0.1005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05598858265665224</v>
+        <v>-0.05314329502052956</v>
       </c>
       <c r="J9" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K9" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01284946444924207</v>
+        <v>0.01170773442016815</v>
       </c>
       <c r="M9" t="n">
-        <v>3.021243485579551</v>
+        <v>3.018326398924766</v>
       </c>
       <c r="N9" t="n">
-        <v>13.87196140418752</v>
+        <v>13.82805655112856</v>
       </c>
       <c r="O9" t="n">
-        <v>3.724508209708702</v>
+        <v>3.718609491614918</v>
       </c>
       <c r="P9" t="n">
-        <v>187.1728840705224</v>
+        <v>187.142473459112</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37023,28 +37231,28 @@
         <v>0.1107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1196309400577381</v>
+        <v>-0.1165536841876821</v>
       </c>
       <c r="J10" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K10" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07080258916178495</v>
+        <v>0.06800242413697477</v>
       </c>
       <c r="M10" t="n">
-        <v>2.687137015117405</v>
+        <v>2.685679609493453</v>
       </c>
       <c r="N10" t="n">
-        <v>10.87149065553783</v>
+        <v>10.85146134638113</v>
       </c>
       <c r="O10" t="n">
-        <v>3.297194361201327</v>
+        <v>3.294155634814652</v>
       </c>
       <c r="P10" t="n">
-        <v>188.4118066921846</v>
+        <v>188.3790310650633</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37095,28 +37303,28 @@
         <v>0.1286</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02021934450133092</v>
+        <v>0.0273426082294119</v>
       </c>
       <c r="J11" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="K11" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001348738306890751</v>
+        <v>0.002462655985783102</v>
       </c>
       <c r="M11" t="n">
-        <v>3.353156701691572</v>
+        <v>3.375883052571463</v>
       </c>
       <c r="N11" t="n">
-        <v>17.52118684735828</v>
+        <v>17.65026060825528</v>
       </c>
       <c r="O11" t="n">
-        <v>4.185831679291259</v>
+        <v>4.201221323407668</v>
       </c>
       <c r="P11" t="n">
-        <v>191.825134533692</v>
+        <v>191.7492642006277</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37154,7 +37362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79645,6 +79853,254 @@
         </is>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-36.81949618978681,174.80661113710053</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-36.82012806766593,174.80704617722137</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-36.82070824887847,174.80757276609413</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-36.821306899275775,174.80808472281538</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-36.821895901774006,174.80860292745453</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-36.822482999777925,174.80912444256487</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-36.823062380881346,174.80966168564476</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>-36.82371320647398,174.81006441936955</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>-36.82431243685666,174.81056443465812</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>-36.824838224997876,174.81119703569505</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-36.81949575386848,174.8066119878116</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-36.82012835805895,174.80704560990245</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-36.82070773777642,174.80757382257613</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-36.82130719474118,174.8080841595546</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-36.821895310838194,174.80860405398028</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-36.8224838339028,174.80912284418554</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-36.82306368423971,174.80965926370882</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>-36.82371140181217,174.81006777283702</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>-36.824311981772595,174.81056526974788</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>-36.82483780858497,174.81119762512344</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-36.81949696475274,174.80660962472527</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-36.82012951963095,174.8070433406267</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-36.820707273138204,174.80757478301427</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-36.821308869045076,174.80808096774365</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-36.82189545857217,174.80860377234885</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-36.82248344137344,174.80912359636403</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-36.823065238243856,174.80965637601585</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>-36.82371225401359,174.8100661892552</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>-36.82431263911625,174.81056406350712</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>-36.82483763012229,174.8111978777356</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-36.819498611555254,174.8066064109277</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-36.82013082639943,174.80704078769142</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-36.820707830704066,174.8075736304885</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-36.82131206991995,174.80807486575168</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-36.8218986102296,174.80859776421136</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-36.822485551218655,174.80911955340449</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-36.82306704289375,174.8096530225658</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>-36.82371375789841,174.81006339469891</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>-36.82431284137583,174.8105636923561</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>-36.82483911731123,174.81119577263422</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0599/nzd0599.xlsx
+++ b/data/nzd0599/nzd0599.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L690"/>
+  <dimension ref="A1:L691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29406,6 +29406,48 @@
       <c r="L690" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="C691" t="n">
+        <v>175.63</v>
+      </c>
+      <c r="D691" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="E691" t="n">
+        <v>185.99</v>
+      </c>
+      <c r="F691" t="n">
+        <v>189.35</v>
+      </c>
+      <c r="G691" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="H691" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="I691" t="n">
+        <v>188.35</v>
+      </c>
+      <c r="J691" t="n">
+        <v>187.63</v>
+      </c>
+      <c r="K691" t="n">
+        <v>198.7</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29420,7 +29462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B707"/>
+  <dimension ref="A1:B708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36493,6 +36535,16 @@
       </c>
       <c r="B707" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>
@@ -36655,28 +36707,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2333446440260231</v>
+        <v>0.2321216062401417</v>
       </c>
       <c r="J2" t="n">
+        <v>690</v>
+      </c>
+      <c r="K2" t="n">
         <v>689</v>
       </c>
-      <c r="K2" t="n">
-        <v>688</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.08858949524464732</v>
+        <v>0.087932803227326</v>
       </c>
       <c r="M2" t="n">
-        <v>4.557865214621564</v>
+        <v>4.557460514635589</v>
       </c>
       <c r="N2" t="n">
-        <v>32.49220111257803</v>
+        <v>32.47226045815056</v>
       </c>
       <c r="O2" t="n">
-        <v>5.700193076780648</v>
+        <v>5.698443687372067</v>
       </c>
       <c r="P2" t="n">
-        <v>178.5069965365435</v>
+        <v>178.5201142583279</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36727,28 +36779,28 @@
         <v>0.0997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3429105817570017</v>
+        <v>0.3433413536907064</v>
       </c>
       <c r="J3" t="n">
+        <v>690</v>
+      </c>
+      <c r="K3" t="n">
         <v>689</v>
       </c>
-      <c r="K3" t="n">
-        <v>688</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2359471303702564</v>
+        <v>0.236948392890175</v>
       </c>
       <c r="M3" t="n">
-        <v>3.748353689576303</v>
+        <v>3.745013360972057</v>
       </c>
       <c r="N3" t="n">
-        <v>22.08625803128373</v>
+        <v>22.0575790192896</v>
       </c>
       <c r="O3" t="n">
-        <v>4.699601901361831</v>
+        <v>4.696549693050165</v>
       </c>
       <c r="P3" t="n">
-        <v>164.7843624278601</v>
+        <v>164.7797421729146</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36799,28 +36851,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6246400388317364</v>
+        <v>0.6259867959324464</v>
       </c>
       <c r="J4" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K4" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6731514461222565</v>
+        <v>0.6741378403364542</v>
       </c>
       <c r="M4" t="n">
-        <v>2.689065003885605</v>
+        <v>2.691956865532787</v>
       </c>
       <c r="N4" t="n">
-        <v>11.01781800813286</v>
+        <v>11.03490114883451</v>
       </c>
       <c r="O4" t="n">
-        <v>3.319309869254882</v>
+        <v>3.321882169619283</v>
       </c>
       <c r="P4" t="n">
-        <v>160.7856190791054</v>
+        <v>160.7711878693102</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36871,28 +36923,28 @@
         <v>0.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6371063131407035</v>
+        <v>0.6384921020774955</v>
       </c>
       <c r="J5" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K5" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7289040052987708</v>
+        <v>0.7296033417402034</v>
       </c>
       <c r="M5" t="n">
-        <v>2.32733728649261</v>
+        <v>2.330841960337622</v>
       </c>
       <c r="N5" t="n">
-        <v>8.768074121376173</v>
+        <v>8.790335689236286</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9610933996374</v>
+        <v>2.96485002811884</v>
       </c>
       <c r="P5" t="n">
-        <v>163.7688633620556</v>
+        <v>163.754007007045</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36943,28 +36995,28 @@
         <v>0.1228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5207987715039039</v>
+        <v>0.5226343866800029</v>
       </c>
       <c r="J6" t="n">
+        <v>690</v>
+      </c>
+      <c r="K6" t="n">
         <v>689</v>
       </c>
-      <c r="K6" t="n">
-        <v>688</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.6629150651310777</v>
+        <v>0.6634911231437517</v>
       </c>
       <c r="M6" t="n">
-        <v>2.29740430887078</v>
+        <v>2.303672103367644</v>
       </c>
       <c r="N6" t="n">
-        <v>7.999687332095369</v>
+        <v>8.049387579064588</v>
       </c>
       <c r="O6" t="n">
-        <v>2.828371851807214</v>
+        <v>2.83714426476071</v>
       </c>
       <c r="P6" t="n">
-        <v>168.6881394174622</v>
+        <v>168.6684514818471</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37015,28 +37067,28 @@
         <v>0.1034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4500943797259051</v>
+        <v>0.4517198029106695</v>
       </c>
       <c r="J7" t="n">
+        <v>690</v>
+      </c>
+      <c r="K7" t="n">
         <v>689</v>
       </c>
-      <c r="K7" t="n">
-        <v>688</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.6253370360541654</v>
+        <v>0.6261760383394415</v>
       </c>
       <c r="M7" t="n">
-        <v>2.15595261355287</v>
+        <v>2.16060374587897</v>
       </c>
       <c r="N7" t="n">
-        <v>7.04020734083831</v>
+        <v>7.078062947037485</v>
       </c>
       <c r="O7" t="n">
-        <v>2.653338904255977</v>
+        <v>2.660462919688505</v>
       </c>
       <c r="P7" t="n">
-        <v>175.1105723267216</v>
+        <v>175.0931388104675</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37087,28 +37139,28 @@
         <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1388810254864987</v>
+        <v>0.141770294915834</v>
       </c>
       <c r="J8" t="n">
+        <v>690</v>
+      </c>
+      <c r="K8" t="n">
         <v>689</v>
       </c>
-      <c r="K8" t="n">
-        <v>688</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1172007709671192</v>
+        <v>0.1199682677015766</v>
       </c>
       <c r="M8" t="n">
-        <v>2.171062707229928</v>
+        <v>2.185082809912015</v>
       </c>
       <c r="N8" t="n">
-        <v>8.426921766314761</v>
+        <v>8.566588376308859</v>
       </c>
       <c r="O8" t="n">
-        <v>2.902916079791967</v>
+        <v>2.926873481431826</v>
       </c>
       <c r="P8" t="n">
-        <v>183.5754682338955</v>
+        <v>183.544479303732</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37159,28 +37211,28 @@
         <v>0.1005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05314329502052956</v>
+        <v>-0.05239530264188042</v>
       </c>
       <c r="J9" t="n">
+        <v>690</v>
+      </c>
+      <c r="K9" t="n">
         <v>689</v>
       </c>
-      <c r="K9" t="n">
-        <v>688</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01170773442016815</v>
+        <v>0.01141182599548607</v>
       </c>
       <c r="M9" t="n">
-        <v>3.018326398924766</v>
+        <v>3.017790584598301</v>
       </c>
       <c r="N9" t="n">
-        <v>13.82805655112856</v>
+        <v>13.81816728197461</v>
       </c>
       <c r="O9" t="n">
-        <v>3.718609491614918</v>
+        <v>3.717279553917705</v>
       </c>
       <c r="P9" t="n">
-        <v>187.142473459112</v>
+        <v>187.1344508485</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37231,28 +37283,28 @@
         <v>0.1107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1165536841876821</v>
+        <v>-0.1158745656928606</v>
       </c>
       <c r="J10" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K10" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06800242413697477</v>
+        <v>0.06741625903492354</v>
       </c>
       <c r="M10" t="n">
-        <v>2.685679609493453</v>
+        <v>2.684944098953969</v>
       </c>
       <c r="N10" t="n">
-        <v>10.85146134638113</v>
+        <v>10.84418568567906</v>
       </c>
       <c r="O10" t="n">
-        <v>3.294155634814652</v>
+        <v>3.293051121024248</v>
       </c>
       <c r="P10" t="n">
-        <v>188.3790310650633</v>
+        <v>188.3717725252018</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37303,28 +37355,28 @@
         <v>0.1286</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0273426082294119</v>
+        <v>0.02908518135884644</v>
       </c>
       <c r="J11" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K11" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002462655985783102</v>
+        <v>0.002785732211551206</v>
       </c>
       <c r="M11" t="n">
-        <v>3.375883052571463</v>
+        <v>3.38152234444234</v>
       </c>
       <c r="N11" t="n">
-        <v>17.65026060825528</v>
+        <v>17.68032266839786</v>
       </c>
       <c r="O11" t="n">
-        <v>4.201221323407668</v>
+        <v>4.204797577577054</v>
       </c>
       <c r="P11" t="n">
-        <v>191.7492642006277</v>
+        <v>191.7306392675445</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37362,7 +37414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L690"/>
+  <dimension ref="A1:L691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80101,6 +80153,68 @@
         </is>
       </c>
     </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-36.81949744910642,174.80660867949072</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-36.82012893884496,174.80704447526458</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-36.820708295342286,174.80757267005035</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-36.821311380500774,174.80807618002692</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-36.82189865947425,174.8085976703342</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-36.82248442269682,174.80912171591777</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>-36.82306634108547,174.8096543266853</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>-36.82371185297763,174.81006693447017</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>-36.82431395380352,174.8105616510255</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>-36.82483840346054,174.8111967830829</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
